--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA79C02-33AC-4A6D-8FE4-FF4816A66526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B9FCE8-B3F8-4223-95BA-7D2B48AFC3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -246,6 +246,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -255,26 +276,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,7 +801,7 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="28" customWidth="1"/>
     <col min="2" max="2" width="19.44140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="24.109375" style="7" customWidth="1"/>
     <col min="4" max="4" width="35.109375" style="7" customWidth="1"/>
@@ -793,29 +811,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="21"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="22"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="23" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -833,12 +851,12 @@
       <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="13" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -847,7 +865,7 @@
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -856,7 +874,7 @@
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="2"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -865,7 +883,7 @@
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="2"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -874,7 +892,7 @@
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -883,7 +901,7 @@
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="2"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -892,7 +910,7 @@
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="2"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -901,7 +919,7 @@
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -910,7 +928,7 @@
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="2"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -919,7 +937,7 @@
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="2"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -928,7 +946,7 @@
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="2"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -952,7 +970,7 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="25" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
@@ -963,31 +981,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="26" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -1013,7 +1031,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -1023,7 +1041,7 @@
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1033,7 +1051,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1043,7 +1061,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1053,7 +1071,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1063,7 +1081,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1073,7 +1091,7 @@
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -1083,7 +1101,7 @@
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1093,7 +1111,7 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1103,7 +1121,7 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -1113,7 +1131,7 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1137,7 +1155,7 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="25" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1148,31 +1166,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="23" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1198,7 +1216,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -1208,7 +1226,7 @@
       <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1218,7 +1236,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1228,7 +1246,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="24"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1238,7 +1256,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1248,7 +1266,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1258,7 +1276,7 @@
       <c r="H9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
+      <c r="A10" s="24"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -1268,7 +1286,7 @@
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
+      <c r="A11" s="24"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1278,7 +1296,7 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
+      <c r="A12" s="24"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1288,7 +1306,7 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -1298,7 +1316,7 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1308,7 +1326,7 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
+      <c r="A15" s="24"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -1318,7 +1336,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -1328,7 +1346,7 @@
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
+      <c r="A17" s="24"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -1338,7 +1356,7 @@
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -1348,7 +1366,7 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B9FCE8-B3F8-4223-95BA-7D2B48AFC3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F5D47E-BD3B-48B8-8EA3-CCD98A0C495F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Images</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -218,9 +221,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -246,8 +248,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -276,23 +293,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -315,13 +329,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>3301365</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1257299</xdr:rowOff>
@@ -798,166 +812,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="28" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="35.109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="23" style="8" customWidth="1"/>
-    <col min="6" max="6" width="48.88671875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="13" style="17" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23" style="7" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="2" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="23"/>
+    </row>
+    <row r="3" spans="1:8" s="31" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="9"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -970,7 +1001,7 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="25" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="14" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" customWidth="1"/>
@@ -981,164 +1012,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="26" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1155,7 +1186,7 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="14" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1166,214 +1197,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:8" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F5D47E-BD3B-48B8-8EA3-CCD98A0C495F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76B10FE-BF1B-408A-8B86-D767A26607BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regular service" sheetId="1" r:id="rId1"/>
@@ -145,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -168,89 +168,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -258,31 +182,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -293,20 +214,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,178 +742,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="13" style="17" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="23" style="7" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="13" style="15" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="17" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="23" style="18" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="18" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="19" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:8" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-    </row>
-    <row r="3" spans="1:8" s="31" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1001,42 +822,43 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="28" style="19" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="19" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" style="19" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="19" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="19" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -1062,114 +884,114 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1186,7 +1008,7 @@
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="14" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -1197,46 +1019,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="9" t="s">
@@ -1247,164 +1069,164 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76B10FE-BF1B-408A-8B86-D767A26607BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993470E3-7665-405E-AF18-EFED3DB2543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12816" yWindow="36" windowWidth="10572" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regular service" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -77,13 +77,25 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>Total Services Done</t>
+  </si>
+  <si>
+    <t>Total Services Missed</t>
+  </si>
+  <si>
+    <t>Total Services Pending</t>
+  </si>
+  <si>
+    <t>Week</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +137,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -172,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -205,6 +225,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -213,30 +260,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,45 +765,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="13" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="23" style="18" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="14.88671875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="13" style="12" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" style="14" customWidth="1"/>
+    <col min="6" max="6" width="23" style="15" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="16" customWidth="1"/>
+    <col min="9" max="10" width="8.88671875" style="16"/>
+    <col min="11" max="11" width="17.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:13" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:13" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+    </row>
+    <row r="3" spans="1:13" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -804,6 +831,18 @@
       </c>
       <c r="H3" s="6" t="s">
         <v>18</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -822,40 +861,40 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="22" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="28" style="19" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="19" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" style="19" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="19.77734375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="28" style="16" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" style="16" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="16" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -884,114 +923,114 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1019,28 +1058,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76B10FE-BF1B-408A-8B86-D767A26607BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69227593-235F-4C1E-955B-52DF210021A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regular service" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -77,13 +77,25 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Regular services Done </t>
+  </si>
+  <si>
+    <t>Total Regular services Missed</t>
+  </si>
+  <si>
+    <t>Total Regular services Pending</t>
+  </si>
+  <si>
+    <t>Total Locations</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -130,8 +142,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,8 +164,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -168,11 +194,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -187,9 +235,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -205,6 +250,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -214,29 +286,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -742,45 +802,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="13" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="16" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="23" style="18" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13" style="11" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="23" style="14" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="18" customWidth="1"/>
+    <col min="9" max="11" width="8.88671875" style="15"/>
+    <col min="12" max="12" width="24.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="25.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -802,9 +866,47 @@
       <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="19" t="s">
         <v>18</v>
       </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L6" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -822,176 +924,176 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="22" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="28" style="19" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="19" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" style="19" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="19" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="19" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="19"/>
+    <col min="1" max="1" width="19.77734375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="28" style="15" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="15" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1019,30 +1121,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1061,10 +1163,10 @@
       <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>13</v>
       </c>
     </row>

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69227593-235F-4C1E-955B-52DF210021A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0E95C6-EEA7-4FA4-94B0-43BDEC449DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -277,6 +277,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -285,18 +294,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
@@ -814,35 +811,35 @@
     <col min="7" max="7" width="48.88671875" style="14" customWidth="1"/>
     <col min="8" max="8" width="13.21875" style="18" customWidth="1"/>
     <col min="9" max="11" width="8.88671875" style="15"/>
-    <col min="12" max="12" width="24.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21" style="15" customWidth="1"/>
     <col min="13" max="14" width="25.109375" style="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -871,42 +868,30 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="23" t="s">
+      <c r="N6" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="23" t="s">
+      <c r="O6" s="20" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -936,28 +921,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
@@ -1121,28 +1106,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993470E3-7665-405E-AF18-EFED3DB2543F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBF4AC5-1A0F-43FA-AF2B-69099E3A8EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12816" yWindow="36" windowWidth="10572" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regular service" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>Total Services Pending</t>
-  </si>
-  <si>
-    <t>Week</t>
   </si>
 </sst>
 </file>
@@ -151,7 +148,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,6 +158,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -192,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -249,9 +252,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -260,6 +260,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -765,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="12" customWidth="1"/>
@@ -779,35 +785,35 @@
     <col min="9" max="10" width="8.88671875" style="16"/>
     <col min="11" max="11" width="17.5546875" style="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="16"/>
+    <col min="13" max="14" width="20" style="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:14" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="2" spans="1:13" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+    </row>
+    <row r="2" spans="1:14" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-    </row>
-    <row r="3" spans="1:13" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+    </row>
+    <row r="3" spans="1:14" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -832,18 +838,23 @@
       <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="20" t="s">
+      <c r="J3" s="23"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="M6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="N6" s="24" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -873,28 +884,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -1058,28 +1069,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0E95C6-EEA7-4FA4-94B0-43BDEC449DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA0A6A0-A24D-455C-85BC-3838C9DF73F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Regular service" sheetId="1" r:id="rId1"/>
-    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId2"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
+    <sheet name="Overview" sheetId="4" r:id="rId1"/>
+    <sheet name="Regular service" sheetId="1" r:id="rId2"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -88,7 +89,13 @@
     <t>Total Regular services Pending</t>
   </si>
   <si>
-    <t>Total Locations</t>
+    <t xml:space="preserve">Total Product services Done </t>
+  </si>
+  <si>
+    <t>Total Prouct services Missed</t>
+  </si>
+  <si>
+    <t>Total Product services Pending</t>
   </si>
 </sst>
 </file>
@@ -208,11 +215,11 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -220,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -280,11 +287,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -798,6 +811,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18DC2A7-2F79-4048-9D55-626077173C21}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -811,35 +871,36 @@
     <col min="7" max="7" width="48.88671875" style="14" customWidth="1"/>
     <col min="8" max="8" width="13.21875" style="18" customWidth="1"/>
     <col min="9" max="11" width="8.88671875" style="15"/>
-    <col min="12" max="12" width="21" style="15" customWidth="1"/>
-    <col min="13" max="14" width="25.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.109375" style="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -868,30 +929,13 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="O6" s="20" t="s">
-        <v>23</v>
-      </c>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
+      <c r="O7" s="22"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
+      <c r="O8" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -904,7 +948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -921,28 +965,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
@@ -1090,7 +1134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1106,28 +1150,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,21 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBF4AC5-1A0F-43FA-AF2B-69099E3A8EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9656753-B1B9-4ED5-BE71-DA985B0E7577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Regular service" sheetId="1" r:id="rId1"/>
-    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId2"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId3"/>
+    <sheet name="Overview" sheetId="4" r:id="rId1"/>
+    <sheet name="Regular service" sheetId="1" r:id="rId2"/>
+    <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -79,13 +80,22 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Total Services Done</t>
-  </si>
-  <si>
-    <t>Total Services Missed</t>
-  </si>
-  <si>
     <t>Total Services Pending</t>
+  </si>
+  <si>
+    <t>Total Regular Services Done</t>
+  </si>
+  <si>
+    <t>Total Regular Services Missed</t>
+  </si>
+  <si>
+    <t>Total Regular Services Pending</t>
+  </si>
+  <si>
+    <t>Total Product service Done</t>
+  </si>
+  <si>
+    <t>Total Product services Missed</t>
   </si>
 </sst>
 </file>
@@ -252,6 +262,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -260,12 +276,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -770,8 +780,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81EB87E8-18BC-4CE1-99D4-6F258C3A2888}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="12" customWidth="1"/>
@@ -789,31 +841,31 @@
     <col min="15" max="16384" width="8.88671875" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:14" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+    </row>
+    <row r="2" spans="1:10" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:14" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+    </row>
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -838,23 +890,7 @@
       <c r="H3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="23"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="L6" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
+      <c r="J3" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -867,7 +903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -884,28 +920,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -1053,7 +1089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1069,28 +1105,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA0A6A0-A24D-455C-85BC-3838C9DF73F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB0903-E7B8-4940-8A01-93802CFD22F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -80,29 +80,50 @@
     <t>Time</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Regular services Done </t>
-  </si>
-  <si>
-    <t>Total Regular services Missed</t>
-  </si>
-  <si>
-    <t>Total Regular services Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Product services Done </t>
-  </si>
-  <si>
-    <t>Total Prouct services Missed</t>
-  </si>
-  <si>
-    <t>Total Product services Pending</t>
+    <t>Complaints</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Reopened</t>
+  </si>
+  <si>
+    <t>Close Requested</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total services Done </t>
+  </si>
+  <si>
+    <t>Total services Missed</t>
+  </si>
+  <si>
+    <t>Total services Pending</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Unscheduled Work</t>
+  </si>
+  <si>
+    <t>Casual Work</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,8 +178,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,8 +206,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -205,6 +240,15 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -215,19 +259,34 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -287,18 +346,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -308,6 +372,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,47 +882,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18DC2A7-2F79-4048-9D55-626077173C21}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A2:N9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="F2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="G3" s="25" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="24"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="H3" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="I3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="J3" s="25" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="32"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="36"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -879,28 +1012,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -965,28 +1098,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
@@ -1150,28 +1283,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9656753-B1B9-4ED5-BE71-DA985B0E7577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB0903-E7B8-4940-8A01-93802CFD22F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -80,29 +80,50 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Total Services Pending</t>
-  </si>
-  <si>
-    <t>Total Regular Services Done</t>
-  </si>
-  <si>
-    <t>Total Regular Services Missed</t>
-  </si>
-  <si>
-    <t>Total Regular Services Pending</t>
-  </si>
-  <si>
-    <t>Total Product service Done</t>
-  </si>
-  <si>
-    <t>Total Product services Missed</t>
+    <t>Complaints</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Reopened</t>
+  </si>
+  <si>
+    <t>Close Requested</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total services Done </t>
+  </si>
+  <si>
+    <t>Total services Missed</t>
+  </si>
+  <si>
+    <t>Total services Pending</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Unscheduled Work</t>
+  </si>
+  <si>
+    <t>Casual Work</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,8 +178,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,8 +206,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -201,11 +236,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -220,9 +301,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -262,12 +340,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -277,6 +372,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,92 +881,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81EB87E8-18BC-4CE1-99D4-6F258C3A2888}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18DC2A7-2F79-4048-9D55-626077173C21}">
+  <dimension ref="A2:N9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="F2" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="G3" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="H3" s="25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="I3" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="J3" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="32"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="36"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="12" customWidth="1"/>
-    <col min="2" max="2" width="13" style="12" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="23" style="15" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="16" customWidth="1"/>
-    <col min="9" max="10" width="8.88671875" style="16"/>
-    <col min="11" max="11" width="17.5546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="20" style="16" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13" style="11" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" style="13" customWidth="1"/>
+    <col min="5" max="5" width="35.109375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="23" style="14" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" style="14" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="18" customWidth="1"/>
+    <col min="9" max="11" width="8.88671875" style="15"/>
+    <col min="12" max="12" width="25" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-    </row>
-    <row r="2" spans="1:10" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-    </row>
-    <row r="3" spans="1:10" s="7" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -887,10 +1057,18 @@
       <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="20"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O6" s="21"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O7" s="22"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O8" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -908,176 +1086,176 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="16" customWidth="1"/>
-    <col min="3" max="3" width="28" style="16" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" style="16" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="16" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="16" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="1" width="19.77734375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="28" style="15" customWidth="1"/>
+    <col min="4" max="4" width="20.44140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" style="15" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1105,30 +1283,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-    </row>
-    <row r="3" spans="1:8" s="11" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1147,10 +1325,10 @@
       <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>13</v>
       </c>
     </row>

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB0903-E7B8-4940-8A01-93802CFD22F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB034F0-4463-4579-9A37-19DE1321ACA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>Casual Work</t>
+  </si>
+  <si>
+    <t>Pest Count</t>
   </si>
 </sst>
 </file>
@@ -187,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -209,6 +212,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -286,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -357,27 +366,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,13 +417,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>3301365</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1257299</xdr:rowOff>
@@ -888,6 +906,7 @@
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -896,24 +915,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="F2" s="26" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="F2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="24"/>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
@@ -964,27 +983,52 @@
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="E6" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37"/>
+      <c r="N6" s="37"/>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="32"/>
+      <c r="C7" s="27"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="36"/>
+      <c r="C9" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="E6:N6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -992,50 +1036,52 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
     <col min="2" max="2" width="13" style="11" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="23" style="14" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="14" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="18" customWidth="1"/>
-    <col min="9" max="11" width="8.88671875" style="15"/>
-    <col min="12" max="12" width="25" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="15"/>
+    <col min="3" max="4" width="19.44140625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" style="13" customWidth="1"/>
+    <col min="6" max="6" width="35.109375" style="13" customWidth="1"/>
+    <col min="7" max="7" width="23" style="14" customWidth="1"/>
+    <col min="8" max="8" width="48.88671875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" style="18" customWidth="1"/>
+    <col min="10" max="12" width="8.88671875" style="15"/>
+    <col min="13" max="13" width="25" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:16" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+    </row>
+    <row r="2" spans="1:16" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-    </row>
-    <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1046,34 +1092,37 @@
         <v>3</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="I3" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O6" s="21"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O7" s="22"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O8" s="21"/>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P6" s="21"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P7" s="22"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P8" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1098,28 +1147,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
@@ -1283,28 +1332,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB0903-E7B8-4940-8A01-93802CFD22F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6F6395-42EE-4284-9EB2-87E99AA78C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="12420" windowHeight="12240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -117,13 +117,31 @@
   </si>
   <si>
     <t>Casual Work</t>
+  </si>
+  <si>
+    <t>Pest Count</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>SubLocation</t>
+  </si>
+  <si>
+    <t>Pest Name</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>subLocation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,8 +204,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -202,18 +229,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -282,11 +321,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -343,9 +408,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -355,29 +417,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,16 +494,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1257300</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>3301365</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1257299</xdr:rowOff>
+      <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -437,7 +532,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7993380" y="68580"/>
+          <a:off x="11551920" y="0"/>
           <a:ext cx="3301365" cy="1188719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -882,160 +977,227 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18DC2A7-2F79-4048-9D55-626077173C21}">
-  <dimension ref="A2:N9"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+    <row r="1" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="F2" s="26" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="G4" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="25" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="B13" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="D13" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="E13" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="31" t="s">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="32"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="33"/>
-      <c r="C8" s="34"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="35" t="s">
+      <c r="B17" s="25"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="36"/>
+      <c r="B19" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="5">
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
     <col min="2" max="2" width="13" style="11" customWidth="1"/>
     <col min="3" max="3" width="19.44140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" style="13" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="23" style="14" customWidth="1"/>
-    <col min="7" max="7" width="48.88671875" style="14" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" style="18" customWidth="1"/>
-    <col min="9" max="11" width="8.88671875" style="15"/>
-    <col min="12" max="12" width="25" style="15" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="15"/>
+    <col min="4" max="4" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.109375" style="13" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="13" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="23" style="14" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="14" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" style="18" customWidth="1"/>
+    <col min="12" max="14" width="8.88671875" style="15"/>
+    <col min="15" max="15" width="25" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:18" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-    </row>
-    <row r="2" spans="1:15" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46"/>
+    </row>
+    <row r="2" spans="1:18" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-    </row>
-    <row r="3" spans="1:15" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+    </row>
+    <row r="3" spans="1:18" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1046,34 +1208,43 @@
         <v>3</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O6" s="21"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O7" s="22"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="O8" s="21"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R6" s="20"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R7" s="21"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R8" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1098,28 +1269,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
@@ -1283,28 +1454,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB034F0-4463-4579-9A37-19DE1321ACA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6F6395-42EE-4284-9EB2-87E99AA78C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2508" yWindow="0" windowWidth="12420" windowHeight="12240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -120,13 +120,28 @@
   </si>
   <si>
     <t>Pest Count</t>
+  </si>
+  <si>
+    <t>Floor</t>
+  </si>
+  <si>
+    <t>SubLocation</t>
+  </si>
+  <si>
+    <t>Pest Name</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>subLocation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,8 +204,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,12 +224,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,8 +239,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -291,11 +321,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -352,9 +408,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -364,18 +417,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -387,14 +464,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -418,15 +495,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1257300</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>3301365</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1257299</xdr:rowOff>
+      <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -455,7 +532,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7993380" y="68580"/>
+          <a:off x="11551920" y="0"/>
           <a:ext cx="3301365" cy="1188719"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -900,188 +977,227 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F18DC2A7-2F79-4048-9D55-626077173C21}">
-  <dimension ref="A2:N9"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+    <row r="1" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="F2" s="32" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="G4" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="25" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="B13" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="D13" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="E13" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E6" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="26" t="s">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="30" t="s">
+      <c r="B17" s="25"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="31"/>
+      <c r="B19" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E6:N6"/>
+  <mergeCells count="5">
+    <mergeCell ref="G4:L4"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
     <col min="2" max="2" width="13" style="11" customWidth="1"/>
-    <col min="3" max="4" width="19.44140625" style="12" customWidth="1"/>
-    <col min="5" max="5" width="24.109375" style="13" customWidth="1"/>
-    <col min="6" max="6" width="35.109375" style="13" customWidth="1"/>
-    <col min="7" max="7" width="23" style="14" customWidth="1"/>
-    <col min="8" max="8" width="48.88671875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" style="18" customWidth="1"/>
-    <col min="10" max="12" width="8.88671875" style="15"/>
-    <col min="13" max="13" width="25" style="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="15"/>
+    <col min="3" max="3" width="19.44140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.109375" style="13" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="13" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="23" style="14" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="14" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" style="18" customWidth="1"/>
+    <col min="12" max="14" width="8.88671875" style="15"/>
+    <col min="15" max="15" width="25" style="15" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:18" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:16" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="46"/>
+    </row>
+    <row r="2" spans="1:18" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-    </row>
-    <row r="3" spans="1:16" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+    </row>
+    <row r="3" spans="1:18" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1098,31 +1214,37 @@
         <v>6</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="P6" s="21"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="P7" s="22"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="P8" s="21"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R6" s="20"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R7" s="21"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R8" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1147,28 +1269,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
@@ -1332,28 +1454,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6F6395-42EE-4284-9EB2-87E99AA78C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0A4315-468B-4212-BA29-307CB5774FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2508" yWindow="0" windowWidth="12420" windowHeight="12240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8556" yWindow="432" windowWidth="13452" windowHeight="12240" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
     <sheet name="Regular service" sheetId="1" r:id="rId2"/>
     <sheet name="Unscheduled-Work" sheetId="3" r:id="rId3"/>
-    <sheet name="Complaints" sheetId="2" r:id="rId4"/>
+    <sheet name="Casual-Work" sheetId="5" r:id="rId4"/>
+    <sheet name="Complaints" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -135,6 +136,15 @@
   </si>
   <si>
     <t>subLocation</t>
+  </si>
+  <si>
+    <t>Sub Location</t>
+  </si>
+  <si>
+    <t>Seviced Date</t>
+  </si>
+  <si>
+    <t>Image</t>
   </si>
 </sst>
 </file>
@@ -434,6 +444,12 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -455,23 +471,17 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,13 +559,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>1181099</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>952500</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>988679</xdr:rowOff>
@@ -604,13 +614,68 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1440181</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>906781</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1158239</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A45CE6FE-A85A-4C7E-B1B6-9E6D8FB81293}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6560821" y="0"/>
+          <a:ext cx="3726180" cy="1158239"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1232746</xdr:rowOff>
@@ -996,34 +1061,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="A1" s="39"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="G4" s="34" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="G4" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="32" t="s">
@@ -1060,11 +1125,11 @@
       <c r="C6" s="22"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="33" t="s">
@@ -1083,13 +1148,13 @@
       <c r="C10" s="22"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="23" t="s">
@@ -1168,34 +1233,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="46"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="45"/>
     </row>
     <row r="2" spans="1:18" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
     </row>
     <row r="3" spans="1:18" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1254,45 +1319,54 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" style="18" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="28" style="15" customWidth="1"/>
-    <col min="4" max="4" width="20.44140625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" style="15" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="15" customWidth="1"/>
-    <col min="8" max="8" width="14.77734375" style="15" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="15"/>
+    <col min="3" max="3" width="11.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="15" customWidth="1"/>
+    <col min="6" max="6" width="28" style="15" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" style="15" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" style="15" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" style="15" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:11" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-    </row>
-    <row r="2" spans="1:8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+    </row>
+    <row r="2" spans="1:11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="1:8" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+    </row>
+    <row r="3" spans="1:11" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
@@ -1300,25 +1374,34 @@
         <v>17</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="F3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="16"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1327,8 +1410,11 @@
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="16"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
@@ -1337,8 +1423,11 @@
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -1347,8 +1436,11 @@
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
       <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="16"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
@@ -1357,8 +1449,11 @@
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="16"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -1367,8 +1462,11 @@
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="17"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="16"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -1377,8 +1475,11 @@
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -1387,8 +1488,11 @@
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="16"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
@@ -1397,8 +1501,11 @@
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
       <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -1407,8 +1514,11 @@
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="16"/>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -1417,8 +1527,11 @@
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -1427,11 +1540,14 @@
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1439,45 +1555,251 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380E4173-DCE8-4A5E-89DB-635BA4667A2A}">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.77734375" style="18" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="28" style="15" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="15" customWidth="1"/>
+    <col min="7" max="8" width="13.6640625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" customFormat="1" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+    </row>
+    <row r="2" spans="1:9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+    </row>
+    <row r="3" spans="1:9" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" style="3" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="26.44140625" customWidth="1"/>
-    <col min="6" max="6" width="19.44140625" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="26.44140625" customWidth="1"/>
+    <col min="8" max="8" width="19.44140625" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+    </row>
+    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-    </row>
-    <row r="3" spans="1:8" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1491,19 +1813,25 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1512,8 +1840,10 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1522,8 +1852,10 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1532,8 +1864,10 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1542,8 +1876,10 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1552,8 +1888,10 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1562,8 +1900,10 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1572,8 +1912,10 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1582,8 +1924,10 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1592,8 +1936,10 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1602,8 +1948,10 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1612,8 +1960,10 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1622,8 +1972,10 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1632,8 +1984,10 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1642,8 +1996,10 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1652,8 +2008,10 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1662,11 +2020,13 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0A4315-468B-4212-BA29-307CB5774FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE3637-8D5F-4DF6-9DB7-6420B8B13CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8556" yWindow="432" windowWidth="13452" windowHeight="12240" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -102,18 +102,6 @@
     <t>Product</t>
   </si>
   <si>
-    <t xml:space="preserve">Total services Done </t>
-  </si>
-  <si>
-    <t>Total services Missed</t>
-  </si>
-  <si>
-    <t>Total services Pending</t>
-  </si>
-  <si>
-    <t>Regular</t>
-  </si>
-  <si>
     <t>Unscheduled Work</t>
   </si>
   <si>
@@ -145,6 +133,36 @@
   </si>
   <si>
     <t>Image</t>
+  </si>
+  <si>
+    <t>Calibration</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Used</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Highest Location Pest Count</t>
+  </si>
+  <si>
+    <t>Total  Missed</t>
+  </si>
+  <si>
+    <t>Regular services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Done </t>
+  </si>
+  <si>
+    <t>Total Pending</t>
+  </si>
+  <si>
+    <t>Total Missed</t>
   </si>
 </sst>
 </file>
@@ -361,12 +379,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -379,12 +394,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -404,12 +413,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -437,51 +440,65 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,8 +527,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>55245</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1188719</xdr:rowOff>
     </xdr:to>
@@ -1050,7 +1067,7 @@
     <col min="3" max="3" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" customWidth="1"/>
     <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -1061,28 +1078,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
       <c r="G4" s="36" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H4" s="36"/>
       <c r="I4" s="36"/>
@@ -1090,86 +1107,86 @@
       <c r="K4" s="36"/>
       <c r="L4" s="36"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="30" t="s">
+    <row r="5" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="31" t="s">
-        <v>37</v>
+      <c r="K5" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="43" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="8" spans="1:13" s="12" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>29</v>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+    </row>
+    <row r="9" spans="1:13" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="18" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1181,20 +1198,20 @@
       <c r="E14" s="1"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="25"/>
+      <c r="A17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="20"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="29"/>
+      <c r="A19" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1211,43 +1228,47 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="13" style="11" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="24.109375" style="13" customWidth="1"/>
-    <col min="7" max="7" width="35.109375" style="13" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" style="13" customWidth="1"/>
-    <col min="9" max="9" width="23" style="14" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" style="14" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" style="18" customWidth="1"/>
-    <col min="12" max="14" width="8.88671875" style="15"/>
-    <col min="15" max="15" width="25" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.77734375" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="15"/>
+    <col min="1" max="1" width="14.88671875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13" style="8" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="24.109375" style="10" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="10" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="23" style="11" customWidth="1"/>
+    <col min="10" max="14" width="12.109375" style="11" customWidth="1"/>
+    <col min="15" max="15" width="13.21875" style="13" customWidth="1"/>
+    <col min="16" max="18" width="8.88671875" style="12"/>
+    <col min="19" max="19" width="25" style="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:22" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="45"/>
-    </row>
-    <row r="2" spans="1:18" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="34"/>
+    </row>
+    <row r="2" spans="1:22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>0</v>
       </c>
@@ -1261,55 +1282,71 @@
       <c r="I2" s="35"/>
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
-    </row>
-    <row r="3" spans="1:18" s="6" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+    </row>
+    <row r="3" spans="1:22" s="5" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R6" s="20"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R7" s="21"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R8" s="20"/>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V6" s="15"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V7" s="16"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V8" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -1319,37 +1356,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95137C80-9D41-4A1F-AAF8-29130318C828}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="18" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="15" customWidth="1"/>
-    <col min="6" max="6" width="28" style="15" customWidth="1"/>
-    <col min="7" max="7" width="20.44140625" style="15" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="17.21875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" style="15" customWidth="1"/>
-    <col min="11" max="11" width="14.77734375" style="15" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="15"/>
+    <col min="1" max="1" width="19.77734375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="28" style="12" customWidth="1"/>
+    <col min="7" max="7" width="20.44140625" style="12" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" style="12" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" style="12" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" style="12" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
     </row>
     <row r="2" spans="1:11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
@@ -1366,183 +1403,40 @@
       <c r="J2" s="35"/>
       <c r="K2" s="35"/>
     </row>
-    <row r="3" spans="1:11" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="29" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1556,32 +1450,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380E4173-DCE8-4A5E-89DB-635BA4667A2A}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" style="18" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="28" style="15" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="15" customWidth="1"/>
-    <col min="7" max="8" width="13.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" style="15" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="15"/>
+    <col min="1" max="1" width="19.77734375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="28" style="12" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="12" customWidth="1"/>
+    <col min="7" max="8" width="13.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" style="12" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="1:9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
@@ -1596,155 +1490,34 @@
       <c r="H2" s="35"/>
       <c r="I2" s="35"/>
     </row>
-    <row r="3" spans="1:9" s="9" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="3" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
+      <c r="I3" s="29" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1758,10 +1531,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D6A6B-C461-47EF-B4E7-783194B4D6F8}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
@@ -1772,18 +1545,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
     </row>
     <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
@@ -1799,229 +1572,37 @@
       <c r="I2" s="35"/>
       <c r="J2" s="35"/>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" s="7" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="29" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -458,6 +458,30 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -470,35 +494,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1078,34 +1078,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="G4" s="36" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="G4" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
     </row>
     <row r="5" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
@@ -1120,19 +1120,19 @@
       <c r="G5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="43" t="s">
+      <c r="I5" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="32" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1142,11 +1142,11 @@
       <c r="C6" s="17"/>
     </row>
     <row r="8" spans="1:13" s="12" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
     </row>
     <row r="9" spans="1:13" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
@@ -1165,13 +1165,13 @@
       <c r="C10" s="17"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="39"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
@@ -1250,42 +1250,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="34"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="42"/>
     </row>
     <row r="2" spans="1:22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
     </row>
     <row r="3" spans="1:22" s="5" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1374,34 +1374,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
     </row>
     <row r="2" spans="1:11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -1465,30 +1465,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -1545,32 +1545,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">

--- a/tmp/dailyReport_Pest.xlsx
+++ b/tmp/dailyReport_Pest.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CE3637-8D5F-4DF6-9DB7-6420B8B13CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025BFA61-8818-4E80-9D7C-8183A490CB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
   <si>
     <t>Contact No:      Email: natco.epcorn@gmail.com / sales@epcorn.com</t>
   </si>
@@ -379,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -458,6 +458,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -470,35 +491,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1078,34 +1084,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="A1" s="35"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="G4" s="36" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="G4" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
     </row>
     <row r="5" spans="1:13" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
@@ -1120,20 +1127,23 @@
       <c r="G5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="43" t="s">
+      <c r="I5" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="43" t="s">
+      <c r="L5" s="32" t="s">
         <v>33</v>
+      </c>
+      <c r="M5" s="47" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1142,11 +1152,11 @@
       <c r="C6" s="17"/>
     </row>
     <row r="8" spans="1:13" s="12" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
     </row>
     <row r="9" spans="1:13" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
@@ -1165,13 +1175,13 @@
       <c r="C10" s="17"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
@@ -1215,11 +1225,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="G4:L4"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="G4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1250,42 +1260,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" customFormat="1" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="34"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="41"/>
     </row>
     <row r="2" spans="1:22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
     </row>
     <row r="3" spans="1:22" s="5" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -1374,34 +1384,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
     </row>
     <row r="2" spans="1:11" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -1465,30 +1475,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
@@ -1545,32 +1555,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
     </row>
     <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:10" s="7" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
